--- a/ValueSet-stroke-circumstance-vs.xlsx
+++ b/ValueSet-stroke-circumstance-vs.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T10:11:46+00:00</t>
+    <t>2026-09-23T10:52:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-stroke-circumstance-vs.xlsx
+++ b/ValueSet-stroke-circumstance-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:36+00:00</t>
+    <t>2026-09-23T10:52:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-stroke-circumstance-vs.xlsx
+++ b/ValueSet-stroke-circumstance-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-23T10:52:57+00:00</t>
+    <t>2026-10-14T14:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-stroke-circumstance-vs.xlsx
+++ b/ValueSet-stroke-circumstance-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T14:44:50+00:00</t>
+    <t>2026-10-15T10:29:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-stroke-circumstance-vs.xlsx
+++ b/ValueSet-stroke-circumstance-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:29:33+00:00</t>
+    <t>2026-10-19T07:01:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-stroke-circumstance-vs.xlsx
+++ b/ValueSet-stroke-circumstance-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T07:01:38+00:00</t>
+    <t>2026-10-28T15:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
